--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTruc_110726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTruc_110726.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4042D1-0C2D-484B-8C04-DEBABC749B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFA9D09-C8C7-465D-9FC3-68EB2B95E100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$23</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -136,6 +123,12 @@
   </si>
   <si>
     <t>006011074331976</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Khách hàng đã đồng ý sửa chữa, công nợ ghi KD Lực</t>
   </si>
 </sst>
 </file>
@@ -145,7 +138,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +237,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -404,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -480,15 +486,48 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -546,40 +585,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -954,7 +967,8 @@
     <col min="8" max="8" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="12.5703125" style="3" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="11" max="11" width="37.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
     <col min="13" max="14" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9.140625" style="1"/>
     <col min="26" max="26" width="14" style="1" customWidth="1"/>
@@ -963,82 +977,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="40" t="s">
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="37" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="45"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="46" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="18"/>
@@ -1049,11 +1063,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1063,11 +1077,11 @@
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
@@ -1080,11 +1094,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1125,6 +1139,9 @@
       <c r="J10" s="22" t="s">
         <v>19</v>
       </c>
+      <c r="K10" s="61" t="s">
+        <v>33</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1134,7 +1151,7 @@
       <c r="B11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="28" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="13" t="s">
@@ -1152,31 +1169,35 @@
       <c r="H11" s="13">
         <v>1</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <v>200000</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="27">
         <f>PRODUCT(H11:I11)</f>
         <v>200000</v>
       </c>
+      <c r="K11" s="60" t="s">
+        <v>34</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="27">
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="62">
         <f>SUM(J11:J11)</f>
         <v>200000</v>
       </c>
+      <c r="K12" s="63"/>
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1206,37 +1227,37 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="17"/>
-      <c r="G15" s="59" t="s">
+      <c r="G15" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="59"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="10"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="60" t="s">
+      <c r="G16" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1307,20 +1328,20 @@
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
       <c r="E22" s="9"/>
       <c r="F22" s="14"/>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
       <c r="K22" s="14"/>
       <c r="AA22" s="2"/>
     </row>
@@ -1398,6 +1419,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A15:D15"/>
@@ -1405,16 +1436,6 @@
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
